--- a/New_Structure/02_Channel_identification_and_dimensionality_33_new_structure_stable.xlsx
+++ b/New_Structure/02_Channel_identification_and_dimensionality_33_new_structure_stable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_program\GAIN\DETECTION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_program\GAIN\CrystalCGAIN\New_Structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28956132-D834-46A2-AC62-12AB81572E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5838965D-801F-4C4B-8FA2-AD134D74954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,116 +22,116 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="37">
   <si>
-    <t>optimize_8000022_new_stable.cif</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>optimize_8000028_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8000029_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8000067_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8000220_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8020115_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8036302_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_8046024_new_stable.cif</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>optimize_9000010_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000171_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000182_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000297_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000332_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000347_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000483_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000533_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000550_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000668_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000670_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000682_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000703_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000765_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000805_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000806_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000860_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9000978_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9033061_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9058826_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9074698_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9093157_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9104112_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9119803_new_stable.cif</t>
-  </si>
-  <si>
-    <t>optimize_9311591_new_stable.cif</t>
   </si>
   <si>
     <t>文件名</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>new_stable_01</t>
+  </si>
+  <si>
+    <t>new_stable_02</t>
+  </si>
+  <si>
+    <t>new_stable_03</t>
+  </si>
+  <si>
+    <t>new_stable_04</t>
+  </si>
+  <si>
+    <t>new_stable_05</t>
+  </si>
+  <si>
+    <t>new_stable_06</t>
+  </si>
+  <si>
+    <t>new_stable_07</t>
+  </si>
+  <si>
+    <t>new_stable_08</t>
+  </si>
+  <si>
+    <t>new_stable_09</t>
+  </si>
+  <si>
+    <t>new_stable_10</t>
+  </si>
+  <si>
+    <t>new_stable_11</t>
+  </si>
+  <si>
+    <t>new_stable_12</t>
+  </si>
+  <si>
+    <t>new_stable_13</t>
+  </si>
+  <si>
+    <t>new_stable_14</t>
+  </si>
+  <si>
+    <t>new_stable_15</t>
+  </si>
+  <si>
+    <t>new_stable_16</t>
+  </si>
+  <si>
+    <t>new_stable_17</t>
+  </si>
+  <si>
+    <t>new_stable_18</t>
+  </si>
+  <si>
+    <t>new_stable_19</t>
+  </si>
+  <si>
+    <t>new_stable_20</t>
+  </si>
+  <si>
+    <t>new_stable_21</t>
+  </si>
+  <si>
+    <t>new_stable_22</t>
+  </si>
+  <si>
+    <t>new_stable_23</t>
+  </si>
+  <si>
+    <t>new_stable_24</t>
+  </si>
+  <si>
+    <t>new_stable_25</t>
+  </si>
+  <si>
+    <t>new_stable_26</t>
+  </si>
+  <si>
+    <t>new_stable_27</t>
+  </si>
+  <si>
+    <t>new_stable_28</t>
+  </si>
+  <si>
+    <t>new_stable_29</t>
+  </si>
+  <si>
+    <t>new_stable_30</t>
+  </si>
+  <si>
+    <t>new_stable_31</t>
+  </si>
+  <si>
+    <t>new_stable_32</t>
+  </si>
+  <si>
+    <t>new_stable_33</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1">
         <v>0.1</v>
@@ -558,1652 +558,1652 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I28" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
